--- a/satisfaction_surveys/045_service_customization_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/045_service_customization_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>service_customization_survey_1</t>
+          <t>user_role</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -528,7 +528,11 @@
           <t>What is your role in the business?</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select all that apply</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -543,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>service_customization_survey_2</t>
+          <t>service_choice</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +570,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>service_customization_survey_3</t>
+          <t>service_frequency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,7 +593,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>service_customization_survey_4</t>
+          <t>service_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -607,17 +611,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>service_customization_survey_5</t>
+          <t>day_of_week</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What time do you usually use this service?</t>
+          <t>What day of week do you usually use this service?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +634,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>service_customization_survey_6</t>
+          <t>satisfaction</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>service_customization_survey_6</t>
+          <t>How satisfied are you with the service?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +662,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>service_customization_survey_7</t>
+          <t>favorite_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Which service do you use?</t>
+          <t>What time of day do you usually enjoy?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +680,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>service_customization_survey_8</t>
+          <t>service_satisfaction</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What day of week do you use this service?</t>
+          <t>Service Satisfaction</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +708,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>service_customization_survey_9</t>
+          <t>service_time_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What time of day do you usually use this service</t>
+          <t>What time do you usually use this service?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +726,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>service_customization_survey_10</t>
+          <t>service_satisfaction_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>service_customization_survey_10</t>
+          <t>Service Satisfaction 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +754,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>service_customization_survey_11</t>
+          <t>service_time_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What time of day do you use this service?</t>
+          <t>Service Time 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +777,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>service_customization_survey_12</t>
+          <t>service_customization</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How satisfied are you with the service?</t>
+          <t>How important is service customization for you?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +795,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>service_customization_survey_13</t>
+          <t>service_customization_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is your favorite time of day?</t>
+          <t>What features would you like to see?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +818,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>service_customization_survey_14</t>
+          <t>service_satisfaction_2_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What time of day do you usually use this service?</t>
+          <t>How satisfied are you with the service features?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +841,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>service_customization_survey_15</t>
+          <t>service_satisfaction_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What time do you usually use this service</t>
+          <t>Service Satisfaction 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +864,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>service_customization_survey_16</t>
+          <t>service_time_4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How satisfied are you with the service?</t>
+          <t>Service Time 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +887,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>service_customization_survey_17</t>
+          <t>service_satisfaction_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What time of day do you usually use this service?</t>
+          <t>Service Satisfaction 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,44 +910,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>service_customization_survey_18</t>
+          <t>service_satisfaction_5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What day of week do you usually use this service?</t>
+          <t>Service Satisfaction 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>service_customization_survey_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What time of day do you usually use this service?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -960,10 +941,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
@@ -988,7 +969,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>service_customization_survey_1_choices</t>
+          <t>user_role_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1005,7 +986,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>service_customization_survey_1_choices</t>
+          <t>user_role_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1022,7 +1003,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>service_customization_survey_1_choices</t>
+          <t>user_role_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1039,7 +1020,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>service_customization_survey_2_choices</t>
+          <t>service_choice_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1056,7 +1037,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>service_customization_survey_2_choices</t>
+          <t>service_choice_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1073,7 +1054,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>service_customization_survey_2_choices</t>
+          <t>service_choice_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1090,7 +1071,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>service_customization_survey_3_choices</t>
+          <t>service_frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1107,7 +1088,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>service_customization_survey_3_choices</t>
+          <t>service_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1124,7 +1105,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>service_customization_survey_3_choices</t>
+          <t>service_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1141,391 +1122,238 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>service_customization_survey_7_choices</t>
+          <t>day_of_week_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>service_d</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Service D</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>service_customization_survey_7_choices</t>
+          <t>day_of_week_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>service_e</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Service E</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>service_customization_survey_7_choices</t>
+          <t>day_of_week_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>service_f</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Service F</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>service_customization_survey_8_choices</t>
+          <t>day_of_week_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>monday</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>service_customization_survey_8_choices</t>
+          <t>day_of_week_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tuesday</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>service_customization_survey_8_choices</t>
+          <t>day_of_week_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>wednesday</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>service_customization_survey_8_choices</t>
+          <t>day_of_week_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>thursday</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>service_customization_survey_8_choices</t>
+          <t>favorite_time_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>friday</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>service_customization_survey_8_choices</t>
+          <t>favorite_time_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>saturday</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>service_customization_survey_8_choices</t>
+          <t>favorite_time_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sunday</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>service_customization_survey_10_choices</t>
+          <t>favorite_time_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>service_g</t>
+          <t>night</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Service G</t>
+          <t>Night</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>service_customization_survey_10_choices</t>
+          <t>service_customization_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>service_h</t>
+          <t>feature_a</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Service H</t>
+          <t>Feature A</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>service_customization_survey_10_choices</t>
+          <t>service_customization_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>service_i</t>
+          <t>feature_b</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Service I</t>
+          <t>Feature B</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>service_customization_survey_13_choices</t>
+          <t>service_customization_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>feature_c</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morning</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>service_customization_survey_13_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>afternoon</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Afternoon</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>service_customization_survey_13_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>evening</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Evening</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>service_customization_survey_18_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>monday</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>service_customization_survey_18_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>tuesday</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>service_customization_survey_18_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>wednesday</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>service_customization_survey_18_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>thursday</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>service_customization_survey_18_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>friday</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>service_customization_survey_18_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>saturday</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>service_customization_survey_18_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>sunday</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Sunday</t>
+          <t>Feature C</t>
         </is>
       </c>
     </row>
